--- a/out/MLP-mamba2_repeat_1_000008.xlsx
+++ b/out/MLP-mamba2_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.581772643840161</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.229132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9817726438401608</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.581772643840161</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.581772643840161</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001417218889738433</v>
+        <v>-0.0001406177009765524</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1628112302331682</v>
+        <v>-0.1615427303031176</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.581772643840161</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1616833480040942</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1630752779334805</v>
+        <v>-0.161804835695005</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4398555022719452</v>
+        <v>0.4368418120883298</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7174807797606145</v>
+        <v>0.7127180552363491</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03133964877287428</v>
+        <v>0.03112488739376818</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.339598484212921</v>
+        <v>0.337424834738658</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0549590658675993</v>
+        <v>0.0545825759020717</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4181665084067071</v>
+        <v>0.4154546388544033</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06676846262842821</v>
+        <v>0.06631138356995801</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4967397625604092</v>
+        <v>0.4934896365311984</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01766860810848735</v>
+        <v>0.01754748852435274</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4652229765128137</v>
+        <v>0.462188898311944</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009815811846692567</v>
+        <v>0.009748307293672601</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4671690253386351</v>
+        <v>0.4641215731132007</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02062350323120389</v>
+        <v>0.0204832806673934</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.229132276861947</v>
+        <v>1.180723568071307</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.498614224441865</v>
+        <v>0.4953518032202523</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008099504693912615</v>
+        <v>0.00804379530719415</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.829132276861947</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4941714321281088</v>
+        <v>0.4909395134815944</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005766632962290003</v>
+        <v>0.005726959454181017</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4976023309501314</v>
+        <v>0.4943467978864345</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00226675197566868</v>
+        <v>0.002251815172481378</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.829132276861947</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4963643425121524</v>
+        <v>0.4931172814345592</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001285162820786926</v>
+        <v>0.001275914341784869</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4966652337279529</v>
+        <v>0.4934159798817881</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004858863384249597</v>
+        <v>0.0004823632307329145</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4963519873631957</v>
+        <v>0.4931049431740632</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.00022510073267398</v>
+        <v>0.0002239997722305638</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.496315879815992</v>
+        <v>0.4930690576121218</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.976915590716732e-05</v>
+        <v>7.896183061281334e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4962490224895256</v>
+        <v>0.49300278940305</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4962092564433669</v>
+        <v>0.4929633540933177</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4962042370826737</v>
+        <v>0.4929583347326247</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.49620021903833</v>
+        <v>0.4929542799397891</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-8.167273192660964e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4961977843681392</v>
+        <v>0.4929516625363703</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4961922671261495</v>
+        <v>0.4929461452943806</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4961859431321416</v>
+        <v>0.4929398213003727</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4961805753435632</v>
+        <v>0.4929344535117943</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9817726438401608</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4961806120920549</v>
+        <v>0.492934490260286</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4961807223375305</v>
+        <v>0.4929346005057615</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4961807958345141</v>
+        <v>0.4929346740027452</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4961809795769733</v>
+        <v>0.4929348577452043</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4961825230136297</v>
+        <v>0.4929364011818608</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4961839929533028</v>
+        <v>0.4929378711215339</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4961852424020248</v>
+        <v>0.4929391205702559</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4961866020962221</v>
+        <v>0.4929404802644532</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4961843971867128</v>
+        <v>0.4929382753549439</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4961839929533028</v>
+        <v>0.4929378711215339</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4961831477379908</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4961836989653681</v>
+        <v>0.4929375771335992</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4961833682289417</v>
+        <v>0.4929372463971728</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4961830742410072</v>
+        <v>0.4929369524092383</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4961831477379908</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4961827067560889</v>
+        <v>0.49293658492432</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4961825965106134</v>
+        <v>0.4929364746788444</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.829132276861947</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4961825597621217</v>
+        <v>0.4929364379303527</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4961827067560889</v>
+        <v>0.49293658492432</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4961822290256953</v>
+        <v>0.4929361071939263</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4961831844864825</v>
+        <v>0.4929370626547137</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4961831477379908</v>
+        <v>0.492937025906222</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4961828170015644</v>
+        <v>0.4929366951697955</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4961832579834664</v>
+        <v>0.4929371361516975</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4961826332591053</v>
+        <v>0.4929365114273364</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4961824495166461</v>
+        <v>0.4929363276848772</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4961820452832361</v>
+        <v>0.4929359234514672</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4961812000679241</v>
+        <v>0.4929350782361552</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4961811633194324</v>
+        <v>0.4929350414876635</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4961813103133996</v>
+        <v>0.4929351884816308</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.496181236816416</v>
+        <v>0.4929351149846471</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4961813103133996</v>
+        <v>0.4929351884816308</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4961813470618916</v>
+        <v>0.4929352252301227</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.496181236816416</v>
+        <v>0.4929351149846471</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.496181677798318</v>
+        <v>0.4929355559665491</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.829132276861947</v>
+        <v>-1.023677129033441</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4961815675528424</v>
+        <v>0.4929354457210736</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4961815308043505</v>
+        <v>0.4929354089725816</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4961814573073669</v>
+        <v>0.492935335475598</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4961814205588752</v>
+        <v>0.4929352987271063</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4961812000679241</v>
+        <v>0.4929350782361552</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4961811265709405</v>
+        <v>0.4929350047391716</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4961810530739569</v>
+        <v>0.492934931242188</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.581772643840161</v>
+        <v>-1.623677129033441</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4961810898224488</v>
+        <v>0.4929349679906799</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4961809795769733</v>
+        <v>0.4929348577452043</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4961810898224488</v>
+        <v>0.4929349679906799</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.829132276861947</v>
+        <v>1.780723568071307</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4961813838103833</v>
+        <v>0.4929352619786144</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000008.xlsx
+++ b/out/MLP-mamba2_repeat_1_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.581772643840161</v>
+        <v>0.04480901703604082</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.229132276861947</v>
+        <v>0.3660552936877104</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877103</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.229132276861947</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.229132276861947</v>
+        <v>-0.2764372596156286</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.581772643840161</v>
+        <v>0.5660552936877103</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562858</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877103</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562858</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.07643725961562858</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.2764372596156287</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877103</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562864</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.229132276861947</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.229132276861947</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.581772643840161</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.229132276861947</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.229132276861947</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001417218889738433</v>
+        <v>-0.0001129115489681717</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1628112302331682</v>
+        <v>-0.1297136831023638</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.581772643840161</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.229132276861947</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.229132276861947</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.581772643840161</v>
+        <v>0.3660552936877101</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877101</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1629529521221421</v>
+        <v>-0.1298265946513319</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.829132276861947</v>
+        <v>0.56605529368771</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1630752779334805</v>
+        <v>-0.1299260369474648</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.4398555022719452</v>
+        <v>0.3575718498451119</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.581772643840161</v>
+        <v>0.3660552936877101</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7174807797606145</v>
+        <v>0.5859042137882943</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.03133964877287428</v>
+        <v>0.02547691922713689</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.229132276861947</v>
+        <v>0.3660552936877101</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.339598484212921</v>
+        <v>0.2787126179026873</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0549590658675993</v>
+        <v>0.04467783580011406</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.229132276861947</v>
+        <v>0.3660552936877102</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4181665084067071</v>
+        <v>0.3425828680362289</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.06676846262842821</v>
+        <v>0.05427829408660277</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156289</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4967397625604092</v>
+        <v>0.4064573692895456</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01766860810848735</v>
+        <v>0.01436339656868309</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156289</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4652229765128137</v>
+        <v>0.3808365693302546</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.009815811846692567</v>
+        <v>0.007978514012323096</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.229132276861947</v>
+        <v>0.3660552936877099</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4671690253386351</v>
+        <v>0.3824176118981016</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.02062350323120389</v>
+        <v>0.01676507136547357</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.229132276861947</v>
+        <v>1.008547846991049</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.498614224441865</v>
+        <v>0.4079799782180579</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.008099504693912615</v>
+        <v>0.006583240516270864</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4941714321281088</v>
+        <v>0.4043673864265396</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005766632962290003</v>
+        <v>0.004686823567671491</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877101</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4976023309501314</v>
+        <v>0.407155562415686</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00226675197566868</v>
+        <v>0.001841732030430009</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4963643425121524</v>
+        <v>0.4061481838750816</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001285162820786926</v>
+        <v>0.001043160953566439</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4966652337279529</v>
+        <v>0.4063918813890393</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004858863384249597</v>
+        <v>0.0003942855384317854</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4963519873631957</v>
+        <v>0.4061360861071229</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.00022510073267398</v>
+        <v>0.0001821632753807493</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.496315879815992</v>
+        <v>0.4061057696027835</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.976915590716732e-05</v>
+        <v>6.362265002008783e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4962490224895256</v>
+        <v>0.4060504006362809</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.980325908626812e-05</v>
+        <v>1.551038732133709e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4962092564433669</v>
+        <v>0.406016925284002</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.401629543134059e-06</v>
+        <v>5.016700784839047e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4962042370826737</v>
+        <v>0.4060119096465192</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.677971888793091e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.49620021903833</v>
+        <v>0.4060077094371968</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-1.195152058104458e-07</v>
+        <v>-1.513939432721747e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562875</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4961977843681392</v>
+        <v>0.4060047255580912</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7189298129189675</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4961922671261495</v>
+        <v>0.4059992818130849</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.413072433009741e-06</v>
+        <v>-4.70653621650487e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.07643725961562875</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4961859431321416</v>
+        <v>0.4059932890796545</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562872</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4961805753435632</v>
+        <v>0.4059879212910761</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4961806120920549</v>
+        <v>0.4059879580395678</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4961807223375305</v>
+        <v>0.4059880682850434</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4961807958345141</v>
+        <v>0.405988141782027</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4961809795769733</v>
+        <v>0.4059883255244862</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4961825230136297</v>
+        <v>0.4059898689611426</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4961839929533028</v>
+        <v>0.4059913389008157</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4961852424020248</v>
+        <v>0.4059925883495377</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4961866020962221</v>
+        <v>0.405993948043735</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4961843971867128</v>
+        <v>0.4059917431342257</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4961839929533028</v>
+        <v>0.4059913389008157</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4961831477379908</v>
+        <v>0.4059904936855037</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4961836989653681</v>
+        <v>0.405991044912881</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4961833682289417</v>
+        <v>0.4059907141764546</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4961830742410072</v>
+        <v>0.4059904201885201</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4961831477379908</v>
+        <v>0.4059904936855037</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4961827067560889</v>
+        <v>0.4059900527036018</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4961825965106134</v>
+        <v>0.4059899424581263</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562872</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4961825597621217</v>
+        <v>0.4059899057096346</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4961827067560889</v>
+        <v>0.4059900527036018</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4961822290256953</v>
+        <v>0.4059895749732081</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4961831844864825</v>
+        <v>0.4059905304339954</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562872</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4961831477379908</v>
+        <v>0.4059904936855037</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.7189298129189675</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4961828170015644</v>
+        <v>0.4059901629490773</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4961832579834664</v>
+        <v>0.4059906039309792</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4961826332591053</v>
+        <v>0.4059899792066182</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4961824495166461</v>
+        <v>0.405989795464159</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4961820452832361</v>
+        <v>0.405989391230749</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4961812000679241</v>
+        <v>0.405988546015437</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4961811633194324</v>
+        <v>0.4059885092669453</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562872</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4961813103133996</v>
+        <v>0.4059886562609125</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9817726438401608</v>
+        <v>-0.07643725961562872</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.496181236816416</v>
+        <v>0.4059885827639289</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562875</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4961813103133996</v>
+        <v>0.4059886562609125</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4961813470618916</v>
+        <v>0.4059886930094045</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562881</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.496181236816416</v>
+        <v>0.4059885827639289</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9817726438401608</v>
+        <v>0.5660552936877101</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.496181677798318</v>
+        <v>0.4059890237458308</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.829132276861947</v>
+        <v>-0.07643725961562881</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4961815675528424</v>
+        <v>0.4059889135003553</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.07643725961562881</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4961815308043505</v>
+        <v>0.4059888767518634</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4961814573073669</v>
+        <v>0.4059888032548798</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4961814205588752</v>
+        <v>0.4059887665063881</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4961812000679241</v>
+        <v>0.405988546015437</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4961811265709405</v>
+        <v>0.4059884725184534</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.9189298129189676</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4961810530739569</v>
+        <v>0.4059883990214698</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.581772643840161</v>
+        <v>-0.2764372596156288</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4961810898224488</v>
+        <v>0.4059884357699617</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>1.829132276861947</v>
+        <v>0.5660552936877102</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4961809795769733</v>
+        <v>0.4059883255244862</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4961810898224488</v>
+        <v>0.4059884357699617</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.829132276861947</v>
+        <v>1.208547846991049</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4961813838103833</v>
+        <v>0.4059887297578962</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000008.xlsx
+++ b/out/MLP-mamba2_repeat_1_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.3323925137519836</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.04480901703604082</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.8150537610054016</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.3660552936877104</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.9943242073059082</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.208547846991049</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5209060907363892</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5660552936877103</v>
+        <v>0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.03273287415504456</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.07643725961562864</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.2683734893798828</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.608540952205658</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.1447644978761673</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4919174909591675</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2021616697311401</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.7643865942955017</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.2764372596156286</v>
+        <v>0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3440224528312683</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.5660552936877103</v>
+        <v>0.3</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.63311368227005</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.07643725961562858</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4578799605369568</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5660552936877103</v>
+        <v>0.3</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.8013712763786316</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.07643725961562858</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.06995315104722977</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.07643725961562858</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.255748987197876</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.2395463436841965</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.3486312031745911</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4396937191486359</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2382470518350601</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2764372596156287</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.5501807332038879</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2764372596156287</v>
+        <v>0.3</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.3642292618751526</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.5660552936877103</v>
+        <v>0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.7383753061294556</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.07643725961562864</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.1790498495101929</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.16</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.5036836266517639</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.07643725961562864</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.283003568649292</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.3</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.5467430353164673</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.6060311198234558</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.208547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.6489735841751099</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.208547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.9791039228439331</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.0407307930290699</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.6790369749069214</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.3660552936877102</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.6105028986930847</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.3660552936877102</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.1539579331874847</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.3660552936877102</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.8132535815238953</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.2687779366970062</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4537762701511383</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.16</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.8589943647384644</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.3660552936877102</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.7456197738647461</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.824270486831665</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8956682085990906</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9890095591545105</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.8722688555717468</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001129115489681717</v>
+        <v>-0.0001164229180378607</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1297136831023638</v>
+        <v>-0.1337475717430304</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.001742471009492874</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.8802972435951233</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.03382676467299461</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.477528303861618</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.1520070880651474</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.6352518200874329</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.2541093230247498</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.3660552936877101</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.8561842441558838</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.5660552936877101</v>
+        <v>-0.16</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.5047897100448608</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.208547846991049</v>
+        <v>0.3</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.7080193161964417</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.208547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.6007937788963318</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.208547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.6359906792640686</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.864407479763031</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.208547846991049</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1298265946513319</v>
+        <v>-0.1338639946610683</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.9834239482879639</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.56605529368771</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1299260369474648</v>
+        <v>-0.1339663389616772</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3575718498451119</v>
+        <v>0.3680065402900342</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.029728127643466</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.3660552936877101</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.5859042137882943</v>
+        <v>0.6027538421305714</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02547691922713689</v>
+        <v>0.02622042531677816</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.8601138591766357</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.3660552936877101</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2787126179026873</v>
+        <v>0.2865973152738647</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04467783580011406</v>
+        <v>0.04598156383343387</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.9439207911491394</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.3660552936877102</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3425828680362289</v>
+        <v>0.352331524198567</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05427829408660277</v>
+        <v>0.05586216967802747</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.07282973080873489</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.2764372596156289</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4064573692895456</v>
+        <v>0.4180702920359178</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01436339656868309</v>
+        <v>0.01478252973448952</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.2592888474464417</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.2764372596156289</v>
+        <v>-0.3</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.3808365693302546</v>
+        <v>0.3917015666391195</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.007978514012323096</v>
+        <v>0.008211478094756124</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.9955316781997681</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.3660552936877099</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.3824176118981016</v>
+        <v>0.3933289276994308</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01676507136547357</v>
+        <v>0.01725507988516296</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.7642428874969482</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.008547846991049</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4079799782180579</v>
+        <v>0.4196383949878698</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006583240516270864</v>
+        <v>0.00677580122253687</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8539020419120789</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.5660552936877102</v>
+        <v>-0.16</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4043673864265396</v>
+        <v>0.4159203703824254</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004686823567671491</v>
+        <v>0.004824818378485358</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.09337856620550156</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.5660552936877101</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.407155562415686</v>
+        <v>0.418790168995929</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001841732030430009</v>
+        <v>0.001896047678383832</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.693633496761322</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4061481838750816</v>
+        <v>0.4177536870268404</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001043160953566439</v>
+        <v>0.001073989216906629</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.07196522504091263</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4063918813890393</v>
+        <v>0.4180045100269127</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0003942855384317854</v>
+        <v>0.0004060292307386027</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.1302960515022278</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4061360861071229</v>
+        <v>0.4177417167064734</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001821632753807493</v>
+        <v>0.0001876680775978301</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.05135967582464218</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4061057696027835</v>
+        <v>0.4177107312577246</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.362265002008783e-05</v>
+        <v>6.523730060879578e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.05687439814209938</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4060504006362809</v>
+        <v>0.417654184056432</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.551038732133709e-05</v>
+        <v>1.59873730729961e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.3802074193954468</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.406016925284002</v>
+        <v>0.4176200464866587</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.016700784839047e-06</v>
+        <v>5.49368653649805e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3978542387485504</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4060119096465192</v>
+        <v>0.4176150301045338</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.7977135181427002</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4060077094371968</v>
+        <v>0.4176108298952114</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.2241685092449188</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.07643725961562875</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4060047255580912</v>
+        <v>0.4176078460161057</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.05445751547813416</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.7189298129189675</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4059992818130849</v>
+        <v>0.4176024022710994</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.1457518488168716</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.07643725961562875</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4059932890796545</v>
+        <v>0.417596409537669</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.5448576211929321</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.07643725961562872</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4059879212910761</v>
+        <v>0.4175910417490907</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.465679794549942</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4059879580395678</v>
+        <v>0.4175910784975824</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.6737826466560364</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4059880682850434</v>
+        <v>0.4175911887430579</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5807939171791077</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.405988141782027</v>
+        <v>0.4175912622400415</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.9960915446281433</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4059883255244862</v>
+        <v>0.4175914459825007</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.990954577922821</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4059898689611426</v>
+        <v>0.4175929894191571</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.9264357686042786</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.208547846991049</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4059913389008157</v>
+        <v>0.4175944593588302</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.9311843514442444</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.208547846991049</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4059925883495377</v>
+        <v>0.4175957088075523</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.9942407608032227</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.405993948043735</v>
+        <v>0.4175970685017495</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.003172052558511496</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4059917431342257</v>
+        <v>0.4175948635922402</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.1991409510374069</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4059913389008157</v>
+        <v>0.4175944593588302</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.04553598165512085</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4059904936855037</v>
+        <v>0.4175936141435183</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.07567895948886871</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.405991044912881</v>
+        <v>0.4175941653708956</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.08946582674980164</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4059907141764546</v>
+        <v>0.4175938346344691</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.4500385522842407</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4059904201885201</v>
+        <v>0.4175935406465346</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.0449313260614872</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4059904936855037</v>
+        <v>0.4175936141435183</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>0.3942038416862488</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4059900527036018</v>
+        <v>0.4175931731616163</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2635220289230347</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4059899424581263</v>
+        <v>0.4175930629161408</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.6025625467300415</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.07643725961562872</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4059899057096346</v>
+        <v>0.4175930261676491</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.04440372437238693</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4059900527036018</v>
+        <v>0.4175931731616163</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.9904584884643555</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4059895749732081</v>
+        <v>0.4175926954312227</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.9010744094848633</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4059905304339954</v>
+        <v>0.4175936508920099</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.05380303040146828</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.07643725961562872</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4059904936855037</v>
+        <v>0.4175936141435183</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.304677814245224</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7189298129189675</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4059901629490773</v>
+        <v>0.4175932834070918</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.08205746114253998</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4059906039309792</v>
+        <v>0.4175937243889938</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.0617714487016201</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4059899792066182</v>
+        <v>0.4175930996646327</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.1220403984189034</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.405989795464159</v>
+        <v>0.4175929159221735</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.009869772009551525</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.405989391230749</v>
+        <v>0.4175925116887635</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.1265343874692917</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.2764372596156288</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.405988546015437</v>
+        <v>0.4175916664734515</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.7549452781677246</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2764372596156288</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4059885092669453</v>
+        <v>0.4175916297249598</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.2107681185007095</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.07643725961562872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4059886562609125</v>
+        <v>0.4175917767189271</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.4851540327072144</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.07643725961562872</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4059885827639289</v>
+        <v>0.4175917032219434</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.9169015884399414</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.07643725961562875</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4059886562609125</v>
+        <v>0.4175917767189271</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.05986024439334869</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4059886930094045</v>
+        <v>0.417591813467419</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.955392599105835</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.07643725961562881</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4059885827639289</v>
+        <v>0.4175917032219434</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.1127981469035149</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.5660552936877101</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4059890237458308</v>
+        <v>0.4175921442038454</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.58124178647995</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.07643725961562881</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4059889135003553</v>
+        <v>0.4175920339583699</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.2069898247718811</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.07643725961562881</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4059888767518634</v>
+        <v>0.4175919972098779</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.2473223954439163</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4059888032548798</v>
+        <v>0.4175919237128943</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.1390066146850586</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4059887665063881</v>
+        <v>0.4175918869644026</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1220214441418648</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.405988546015437</v>
+        <v>0.4175916664734515</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.4608364701271057</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9189298129189676</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4059884725184534</v>
+        <v>0.4175915929764679</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3733417391777039</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9189298129189676</v>
+        <v>0.3</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4059883990214698</v>
+        <v>0.4175915194794843</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.1607164591550827</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.2764372596156288</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4059884357699617</v>
+        <v>0.4175915562279762</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.7385452389717102</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.5660552936877102</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4059883255244862</v>
+        <v>0.4175914459825007</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.9324995279312134</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.208547846991049</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4059884357699617</v>
+        <v>0.4175915562279762</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
+        <v>0.7729892730712891</v>
+      </c>
+      <c r="JB126" t="n">
         <v>1</v>
       </c>
-      <c r="JB126" t="n">
-        <v>1.208547846991049</v>
-      </c>
       <c r="JC126" t="n">
-        <v>0.4059887297578962</v>
+        <v>0.4175918502159107</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_1_000008.xlsx
+++ b/out/MLP-mamba2_repeat_1_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.3323925137519836</v>
+        <v>0.3323920071125031</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.1600000000000001</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.03273287415504456</v>
+        <v>0.03273285925388336</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.4399999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.1447644978761673</v>
+        <v>0.1447642743587494</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.4919174909591675</v>
+        <v>0.4919170439243317</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2021616697311401</v>
+        <v>0.2021614015102386</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.5799999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.7643865942955017</v>
+        <v>0.7643861770629883</v>
       </c>
       <c r="JB12" t="n">
         <v>0.3</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3440224528312683</v>
+        <v>0.3440220654010773</v>
       </c>
       <c r="JB13" t="n">
         <v>0.3</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.63311368227005</v>
+        <v>0.6331132650375366</v>
       </c>
       <c r="JB14" t="n">
         <v>0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.4578799605369568</v>
+        <v>0.4578794538974762</v>
       </c>
       <c r="JB15" t="n">
         <v>0.3</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.8013712763786316</v>
+        <v>0.8013713359832764</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.06995315104722977</v>
+        <v>0.06995302438735962</v>
       </c>
       <c r="JB17" t="n">
         <v>0.02000000000000007</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.255748987197876</v>
+        <v>0.2557485699653625</v>
       </c>
       <c r="JB18" t="n">
         <v>-0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.2395463436841965</v>
+        <v>0.2395459562540054</v>
       </c>
       <c r="JB19" t="n">
         <v>-0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.3486312031745911</v>
+        <v>0.3486307859420776</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.8599999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.4396937191486359</v>
+        <v>0.4396932125091553</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.5799999999999998</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2382470518350601</v>
+        <v>0.2382466346025467</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.5799999999999998</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.5501807332038879</v>
+        <v>0.5501801371574402</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.3642292618751526</v>
+        <v>0.364228755235672</v>
       </c>
       <c r="JB24" t="n">
         <v>0.16</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.7383753061294556</v>
+        <v>0.7383748888969421</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.1790498495101929</v>
+        <v>0.1790495663881302</v>
       </c>
       <c r="JB26" t="n">
         <v>0.16</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.5036836266517639</v>
+        <v>0.5036830306053162</v>
       </c>
       <c r="JB27" t="n">
         <v>0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.283003568649292</v>
+        <v>0.2830031216144562</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.5467430353164673</v>
+        <v>0.5467423796653748</v>
       </c>
       <c r="JB29" t="n">
         <v>0.5799999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.6060311198234558</v>
+        <v>0.6060306429862976</v>
       </c>
       <c r="JB30" t="n">
         <v>0.5799999999999998</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.6489735841751099</v>
+        <v>0.6489731073379517</v>
       </c>
       <c r="JB31" t="n">
         <v>0.5799999999999998</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.9791039228439331</v>
+        <v>0.9791040420532227</v>
       </c>
       <c r="JB32" t="n">
         <v>0.5799999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.0407307930290699</v>
+        <v>0.0407308004796505</v>
       </c>
       <c r="JB33" t="n">
         <v>0.7199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.6790369749069214</v>
+        <v>0.6790364384651184</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.6105028986930847</v>
+        <v>0.6105023622512817</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.1539579331874847</v>
+        <v>0.1539576202630997</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.8132535815238953</v>
+        <v>0.8132533431053162</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.4399999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.2687779366970062</v>
+        <v>0.2687774896621704</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.4399999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.4537762701511383</v>
+        <v>0.4537757337093353</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.16</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.8589943647384644</v>
+        <v>0.8589944243431091</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.02000000000000007</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.7456197738647461</v>
+        <v>0.7456197142601013</v>
       </c>
       <c r="JB41" t="n">
         <v>0.8599999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.8956682085990906</v>
+        <v>0.8956682682037354</v>
       </c>
       <c r="JB43" t="n">
         <v>0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.03382676467299461</v>
+        <v>0.03382677212357521</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.7199999999999999</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.1520070880651474</v>
+        <v>0.1520069539546967</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.6352518200874329</v>
+        <v>0.6352516412734985</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.4399999999999999</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.2541093230247498</v>
+        <v>0.2541092038154602</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.5047897100448608</v>
+        <v>0.5047896504402161</v>
       </c>
       <c r="JB54" t="n">
         <v>0.3</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.7080193161964417</v>
+        <v>0.7080193758010864</v>
       </c>
       <c r="JB55" t="n">
         <v>0.5799999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.07282973080873489</v>
+        <v>0.07282974570989609</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.1600000000000001</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.8539020419120789</v>
+        <v>0.8539019227027893</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.16</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.09337856620550156</v>
+        <v>0.09337853640317917</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.4399999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.693633496761322</v>
+        <v>0.6936334371566772</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.5799999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.2241685092449188</v>
+        <v>0.2241688519716263</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.1199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1457518488168716</v>
+        <v>0.145751878619194</v>
       </c>
       <c r="JB79" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.465679794549942</v>
+        <v>0.4656798541545868</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5807939171791077</v>
+        <v>0.5807938575744629</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.04553598165512085</v>
+        <v>0.04553600400686264</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.07567895948886871</v>
+        <v>0.07567892223596573</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.8599999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.08946582674980164</v>
+        <v>0.08946575224399567</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.8599999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.0449313260614872</v>
+        <v>0.04493130743503571</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.8599999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2635220289230347</v>
+        <v>0.2635219991207123</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.9904584884643555</v>
+        <v>0.9904583692550659</v>
       </c>
       <c r="JB100" t="n">
         <v>0.4399999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.05380303040146828</v>
+        <v>0.05380304157733917</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.304677814245224</v>
+        <v>0.3046779036521912</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.08205746114253998</v>
+        <v>0.08205742388963699</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.0617714487016201</v>
+        <v>0.06177147477865219</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.1220403984189034</v>
+        <v>0.1220403835177422</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.1265343874692917</v>
+        <v>0.1265344023704529</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.1127981469035149</v>
+        <v>0.1127981022000313</v>
       </c>
       <c r="JB115" t="n">
         <v>0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.58124178647995</v>
+        <v>0.5812417268753052</v>
       </c>
       <c r="JB116" t="n">
         <v>0.1600000000000001</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.2069898247718811</v>
+        <v>0.2069898545742035</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.7199999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.2473223954439163</v>
+        <v>0.2473223358392715</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.1220214441418648</v>
+        <v>0.1220216378569603</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.1607164591550827</v>
+        <v>0.160716637969017</v>
       </c>
       <c r="JB123" t="n">
         <v>0.5799999999999998</v>
